--- a/output/pdf_financials_xlsx/EDG.xlsx
+++ b/output/pdf_financials_xlsx/EDG.xlsx
@@ -4872,43 +4872,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.844531</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.194531</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.305601</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.305601</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.386421</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.503461</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.503461</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.598991</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.339536</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.407661</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.507164</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.264364</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.281258</v>
       </c>
     </row>
     <row r="93">
@@ -8022,7 +8022,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -8507,7 +8511,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.844531</v>
       </c>
@@ -8949,7 +8957,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EDG.xlsx
+++ b/output/pdf_financials_xlsx/EDG.xlsx
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004632</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001782</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000884</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000879</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00056</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002832</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -969,19 +969,19 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005596</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.041376</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.08643199999999999</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.163442</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.049938</v>
       </c>
     </row>
     <row r="13">
@@ -1754,22 +1754,22 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.275805</v>
+        <v>-0.280437</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.591817</v>
+        <v>-0.593599</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.2223</v>
+        <v>-0.223184</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.760725</v>
+        <v>2.759846</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.05654</v>
+        <v>1.05598</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.414811</v>
+        <v>-4.417643</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -1777,19 +1777,19 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.022329</v>
+        <v>-3.027925</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.322154</v>
+        <v>-2.36353</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.111471</v>
+        <v>-1.197903</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.330144</v>
+        <v>-0.493586</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.384883</v>
+        <v>0.334945</v>
       </c>
     </row>
     <row r="28">
@@ -1854,22 +1854,22 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.275805</v>
+        <v>-0.280437</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.591817</v>
+        <v>-0.593599</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.2223</v>
+        <v>-0.223184</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.760725</v>
+        <v>2.759846</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.05654</v>
+        <v>1.05598</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.414811</v>
+        <v>-4.417643</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -1877,19 +1877,19 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.022329</v>
+        <v>-3.027925</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.322154</v>
+        <v>-2.36353</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.111471</v>
+        <v>-1.197903</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.330144</v>
+        <v>-0.493586</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.384883</v>
+        <v>0.334945</v>
       </c>
     </row>
     <row r="30">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">

--- a/output/pdf_financials_xlsx/EDG.xlsx
+++ b/output/pdf_financials_xlsx/EDG.xlsx
@@ -540,10 +540,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -563,10 +561,8 @@
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>0</v>
@@ -590,10 +586,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -613,10 +607,8 @@
       <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>0</v>
@@ -640,10 +632,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -663,10 +653,8 @@
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
@@ -690,10 +678,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.145638</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.139299</v>
@@ -713,10 +699,8 @@
       <c r="H7" s="3" t="n">
         <v>0.129171</v>
       </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="3" t="n">
+        <v>0.126755</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.144719</v>
@@ -740,10 +724,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -763,10 +745,8 @@
       <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0</v>
@@ -790,10 +770,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -813,10 +791,8 @@
       <c r="H9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0</v>
@@ -840,10 +816,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.145638</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.139299</v>
@@ -863,10 +837,8 @@
       <c r="H10" s="3" t="n">
         <v>0.129171</v>
       </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="3" t="n">
+        <v>0.126755</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.144719</v>
@@ -890,10 +862,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.339009</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.249636</v>
@@ -913,10 +883,8 @@
       <c r="H11" s="3" t="n">
         <v>-0.17896</v>
       </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="3" t="n">
+        <v>-0.278505</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-1.256488</v>
@@ -940,10 +908,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.005551</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.004632</v>
@@ -963,10 +929,8 @@
       <c r="H12" s="3" t="n">
         <v>0.002832</v>
       </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="3" t="n">
+        <v>0.002049</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0.005596</v>
@@ -990,10 +954,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -1013,10 +975,8 @@
       <c r="H13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>-0</v>
@@ -1040,10 +1000,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -1063,10 +1021,8 @@
       <c r="H14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>0</v>
@@ -1090,10 +1046,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -1113,10 +1067,8 @@
       <c r="H15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1140,10 +1092,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.34404</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.275805</v>
@@ -1163,10 +1113,8 @@
       <c r="H16" s="3" t="n">
         <v>-4.414811</v>
       </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="3" t="n">
+        <v>-0.248632</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-3.022329</v>
@@ -1190,10 +1138,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1213,10 +1159,8 @@
       <c r="H17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1384,10 +1328,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.34404</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.275805</v>
@@ -1407,10 +1349,8 @@
       <c r="H20" s="3" t="n">
         <v>-4.414811</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="3" t="n">
+        <v>-0.248632</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-3.022329</v>
@@ -1434,10 +1374,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1457,10 +1395,8 @@
       <c r="H21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -1484,10 +1420,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1507,10 +1441,8 @@
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
@@ -1534,10 +1466,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.34404</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.275805</v>
@@ -1557,10 +1487,8 @@
       <c r="H23" s="3" t="n">
         <v>-4.414811</v>
       </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="3" t="n">
+        <v>-0.248632</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-3.022329</v>
@@ -1584,10 +1512,8 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>0</v>
@@ -1607,10 +1533,8 @@
       <c r="H24" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>-0.03</v>
@@ -1634,10 +1558,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>0</v>
@@ -1657,10 +1579,8 @@
       <c r="H25" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>-0.03</v>
@@ -1748,10 +1668,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.349591</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.280437</v>
@@ -1771,10 +1689,8 @@
       <c r="H27" s="3" t="n">
         <v>-4.417643</v>
       </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="3" t="n">
+        <v>-0.250681</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-3.027925</v>
@@ -1798,10 +1714,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -1821,10 +1735,8 @@
       <c r="H28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0</v>
@@ -1848,10 +1760,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.349591</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.280437</v>
@@ -1871,10 +1781,8 @@
       <c r="H29" s="3" t="n">
         <v>-4.417643</v>
       </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="3" t="n">
+        <v>-0.250681</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-3.027925</v>
@@ -1970,10 +1878,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1993,10 +1899,8 @@
       <c r="H31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -3644,43 +3548,43 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.07905</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.020783</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0171</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0168</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.01695</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.01655</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.017377</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.015645</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.0189</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.024045</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.026775</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.059622</v>
       </c>
     </row>
     <row r="68">
@@ -5154,10 +5058,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.34404</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.275805</v>
@@ -5177,10 +5079,8 @@
       <c r="H99" s="3" t="n">
         <v>-4.414811</v>
       </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="3" t="n">
+        <v>-0.248632</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-3.022329</v>
@@ -5204,10 +5104,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -5227,10 +5125,8 @@
       <c r="H100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>0</v>
@@ -5254,10 +5150,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.053069</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0.00067</v>
@@ -5277,10 +5171,8 @@
       <c r="H101" s="3" t="n">
         <v>0.003197</v>
       </c>
-      <c r="I101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="3" t="n">
+        <v>0.000522</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>-0.395048</v>
@@ -5304,10 +5196,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -5327,10 +5217,8 @@
       <c r="H102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J102" s="3" t="n">
         <v>0</v>
@@ -5354,10 +5242,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.000481</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0.002851</v>
@@ -5377,10 +5263,8 @@
       <c r="H103" s="3" t="n">
         <v>-0.000425</v>
       </c>
-      <c r="I103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="3" t="n">
+        <v>-0.000959</v>
       </c>
       <c r="J103" s="3" t="n">
         <v>-0.002712</v>
@@ -5404,10 +5288,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.024714</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>-0.042195</v>
@@ -5427,10 +5309,8 @@
       <c r="H104" s="3" t="n">
         <v>-0.0425</v>
       </c>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="3" t="n">
+        <v>0.042662</v>
       </c>
       <c r="J104" s="3" t="n">
         <v>0.012853</v>
@@ -5454,10 +5334,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -5477,10 +5355,8 @@
       <c r="H105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J105" s="3" t="n">
         <v>0</v>
@@ -5504,10 +5380,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.027874</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.038674</v>
@@ -5527,10 +5401,8 @@
       <c r="H106" s="3" t="n">
         <v>-0.039728</v>
       </c>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="3" t="n">
+        <v>0.042225</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>-0.384907</v>
@@ -5554,10 +5426,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -5572,15 +5442,13 @@
         <v>0.08082</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>0.11704</v>
       </c>
       <c r="H107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J107" s="3" t="n">
         <v>0.826599</v>
@@ -5604,10 +5472,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -5627,10 +5493,8 @@
       <c r="H108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J108" s="3" t="n">
         <v>0</v>
@@ -5654,10 +5518,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -5677,10 +5539,8 @@
       <c r="H109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
         <v>0</v>
@@ -5704,10 +5564,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -5727,10 +5585,8 @@
       <c r="H110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -5754,10 +5610,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -5777,10 +5631,8 @@
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -5804,10 +5656,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -5827,10 +5677,8 @@
       <c r="H112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -5854,10 +5702,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -5877,10 +5723,8 @@
       <c r="H113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J113" s="3" t="n">
         <v>0</v>
@@ -5904,10 +5748,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -5927,10 +5769,8 @@
       <c r="H114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -5954,10 +5794,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -5969,33 +5807,31 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.197205</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.505717</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.475831</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>0.05949</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.00576</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.031828</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.032259</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>1.920552</v>
       </c>
     </row>
     <row r="116">
@@ -6004,10 +5840,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -6027,10 +5861,8 @@
       <c r="H116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -6054,10 +5886,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -6077,10 +5907,8 @@
       <c r="H117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J117" s="3" t="n">
         <v>0</v>
@@ -6104,10 +5932,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>-0.319506</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>-0.509541</v>
@@ -6125,12 +5951,10 @@
         <v>-0.439322</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-0.338075</v>
-      </c>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.329975</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>-0.135228</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>-1.326282</v>
@@ -6154,10 +5978,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.078945</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>-0.502129</v>
@@ -6169,7 +5991,7 @@
         <v>-0.083551</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>-0.500925</v>
+        <v>-0.30372</v>
       </c>
       <c r="G119" s="3" t="n">
         <v>0.066955</v>
@@ -6177,10 +5999,8 @@
       <c r="H119" s="3" t="n">
         <v>0.140588</v>
       </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="3" t="n">
+        <v>-0.08760900000000001</v>
       </c>
       <c r="J119" s="3" t="n">
         <v>-1.423183</v>
@@ -6204,10 +6024,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -6227,10 +6045,8 @@
       <c r="H120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
@@ -6254,10 +6070,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -6277,10 +6091,8 @@
       <c r="H121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
         <v>0</v>
@@ -6304,10 +6116,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -6327,10 +6137,8 @@
       <c r="H122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J122" s="3" t="n">
         <v>0</v>
@@ -6354,10 +6162,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -6377,10 +6183,8 @@
       <c r="H123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
         <v>0</v>
@@ -6404,10 +6208,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -6427,10 +6229,8 @@
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -6454,10 +6254,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -6477,10 +6275,8 @@
       <c r="H125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
@@ -6504,10 +6300,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -6527,10 +6321,8 @@
       <c r="H126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>0</v>
@@ -6626,10 +6418,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>-0.008624</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>-0.00636</v>
@@ -6649,10 +6439,8 @@
       <c r="H128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J128" s="3" t="n">
         <v>-0.132553</v>
@@ -6676,10 +6464,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.491376</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.49364</v>
@@ -6699,10 +6485,8 @@
       <c r="H129" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J129" s="3" t="n">
         <v>2.246647</v>
@@ -6726,10 +6510,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.369747</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.553433</v>
@@ -6749,10 +6531,8 @@
       <c r="H130" s="3" t="n">
         <v>0.018639</v>
       </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="3" t="n">
+        <v>0.280539</v>
       </c>
       <c r="J130" s="3" t="n">
         <v>0.505199</v>
@@ -6776,10 +6556,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -6799,10 +6577,8 @@
       <c r="H131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
         <v>0</v>
@@ -6826,10 +6602,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.183686</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.320257</v>
@@ -6849,10 +6623,8 @@
       <c r="H132" s="3" t="n">
         <v>0.2619</v>
       </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I132" s="3" t="n">
+        <v>-0.228359</v>
       </c>
       <c r="J132" s="3" t="n">
         <v>0.008668</v>
@@ -6876,10 +6648,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.553433</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.233176</v>
@@ -6899,10 +6669,8 @@
       <c r="H133" s="3" t="n">
         <v>0.280539</v>
       </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="3" t="n">
+        <v>0.05218</v>
       </c>
       <c r="J133" s="3" t="n">
         <v>0.513867</v>
@@ -6926,10 +6694,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -6949,10 +6715,8 @@
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -6976,10 +6740,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.228745</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.311768</v>
@@ -6991,7 +6753,7 @@
         <v>-0.125721</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>0.003592</v>
+        <v>-0.193613</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.116712</v>
@@ -6999,10 +6761,8 @@
       <c r="H135" s="3" t="n">
         <v>-0.218688</v>
       </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="3" t="n">
+        <v>-0.14075</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-0.814796</v>
@@ -7031,7 +6791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q148"/>
+  <dimension ref="A1:Q170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9625,10 +9385,8 @@
       <c r="I36" s="5" t="n">
         <v>0.08082</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J36" s="5" t="n">
+        <v>0.11704</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -9692,12 +9450,10 @@
         <v>-0.013146</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>-2.902375</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.09958</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>-1.173043</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -9840,10 +9596,8 @@
       <c r="I39" s="5" t="n">
         <v>-0.000879</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J39" s="5" t="n">
+        <v>-0.00056</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -9913,10 +9667,8 @@
       <c r="I40" s="5" t="n">
         <v>-0.000531</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J40" s="5" t="n">
+        <v>-0.001244</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -9984,10 +9736,8 @@
       <c r="I41" s="5" t="n">
         <v>-0.010074</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J41" s="5" t="n">
+        <v>0.007563</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -10055,10 +9805,8 @@
       <c r="I42" s="5" t="n">
         <v>-0.000623</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J42" s="5" t="n">
+        <v>0.142563</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -10123,15 +9871,11 @@
       <c r="H43" s="5" t="n">
         <v>-0.125721</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="5" t="n">
+        <v>-0.193613</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>-0.116712</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -10258,7 +10002,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -10494,15 +10242,11 @@
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -10573,15 +10317,11 @@
           <t>NetOtherFinancingCharges</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="5" t="n">
+        <v>-0.008624</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>-0.00636</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -10808,15 +10548,11 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="5" t="n">
+        <v>0.369747</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.553433</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -10885,15 +10621,11 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="5" t="n">
+        <v>0.553433</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.233176</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -11634,15 +11366,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K62" s="5" t="n">
+        <v>-0.11816</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0.024626</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -11866,10 +11594,8 @@
       <c r="K65" s="5" t="n">
         <v>-0.338075</v>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L65" s="5" t="n">
+        <v>-0.149148</v>
       </c>
       <c r="M65" s="5" t="n">
         <v>-1.406779</v>
@@ -11907,7 +11633,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -11928,10 +11658,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="5" t="n">
+        <v>0.197205</v>
       </c>
       <c r="J66" s="5" t="n">
         <v>0.505717</v>
@@ -11939,10 +11667,8 @@
       <c r="K66" s="5" t="n">
         <v>0.475831</v>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L66" s="5" t="n">
+        <v>0.05949</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -12172,10 +11898,8 @@
       <c r="K69" s="5" t="n">
         <v>0.002832</v>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L69" s="5" t="n">
+        <v>0.002049</v>
       </c>
       <c r="M69" s="5" t="n">
         <v>0.005596</v>
@@ -12327,15 +12051,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K71" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>2.9e-05</v>
       </c>
       <c r="M71" s="5" t="n">
         <v>0.002023</v>
@@ -12402,15 +12122,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K72" s="5" t="n">
+        <v>-4.414811</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>-0.248632</v>
       </c>
       <c r="M72" s="5" t="n">
         <v>-3.022329</v>
@@ -12639,15 +12355,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K75" s="5" t="n">
+        <v>0.140588</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-0.08760900000000001</v>
       </c>
       <c r="M75" s="5" t="n">
         <v>-1.423183</v>
@@ -12692,15 +12404,11 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E76" s="5" t="n">
+        <v>0.491376</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.49364</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -12841,19 +12549,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) OPERATING ACTIVITIES</t>
+          <t>Share‐based compensation                                                       95,530                       ‐</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Net income (loss) for the year $</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Unrealized (gain) loss on marketable securities</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -12869,22 +12573,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H78" s="5" t="n">
-        <v>-0.2223</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>2.760725</v>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>1.05654</v>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-4.414811</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.348743</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>-0.06637</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -12920,15 +12628,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                                                                           ‐          117,040</t>
+          <t>Share‐based compensation                                                       95,530                       ‐</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Unrealized (gain) loss on marketable securities</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Write‐off of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -12954,16 +12666,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J79" s="5" t="n">
-        <v>-1.173043</v>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>4.348743</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0081</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>0.01392</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -12999,7 +12711,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Write‐off of exploration and evaluation assets                                        8,100                         ‐</t>
+          <t>Share‐based compensation                                                       95,530                       ‐</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13033,16 +12745,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J80" s="5" t="n">
-        <v>-0.00056</v>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K80" s="5" t="n">
         <v>-0.002832</v>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="5" t="n">
+        <v>-0.002049</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -13091,10 +12803,8 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" s="5" t="n">
+        <v>-0.000481</v>
       </c>
       <c r="F81" s="5" t="n">
         <v>0.002851</v>
@@ -13118,10 +12828,8 @@
       <c r="K81" s="5" t="n">
         <v>-0.000425</v>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L81" s="5" t="n">
+        <v>-0.000959</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -13170,10 +12878,8 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" s="5" t="n">
+        <v>0.053069</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>0.00067</v>
@@ -13197,10 +12903,8 @@
       <c r="K82" s="5" t="n">
         <v>0.003197</v>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L82" s="5" t="n">
+        <v>0.000522</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -13249,10 +12953,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" s="5" t="n">
+        <v>-0.024714</v>
       </c>
       <c r="F83" s="5" t="n">
         <v>-0.042195</v>
@@ -13276,10 +12978,8 @@
       <c r="K83" s="5" t="n">
         <v>-0.0425</v>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L83" s="5" t="n">
+        <v>0.042662</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -13328,10 +13028,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" s="5" t="n">
+        <v>-0.228745</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>-0.311768</v>
@@ -13355,10 +13053,8 @@
       <c r="K84" s="5" t="n">
         <v>-0.218688</v>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L84" s="5" t="n">
+        <v>-0.14075</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -13394,19 +13090,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) INVESTING ACTIVITIES</t>
+          <t>Net cash provided by financing activities                                                                               ‐         340,000</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Net cash from investing activities</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Net increase (decrease) in cash and cash equivalents during the year</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -13432,16 +13124,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J85" s="5" t="n">
-        <v>0.066955</v>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K85" s="5" t="n">
-        <v>0.140588</v>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2619</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>-0.228359</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -13477,15 +13169,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities                                             340,000                         ‐</t>
+          <t>Net cash provided by financing activities                                                                               ‐         340,000</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in cash and cash equivalents during the year</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -13511,16 +13207,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J86" s="5" t="n">
-        <v>-0.049757</v>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K86" s="5" t="n">
-        <v>0.2619</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.018639</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>0.280539</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -13556,17 +13252,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities                                             340,000                         ‐</t>
+          <t>Net cash provided by financing activities                                                                               ‐         340,000</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Cash and cash equivalents, end of year $</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13594,16 +13290,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J87" s="5" t="n">
-        <v>0.068396</v>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K87" s="5" t="n">
-        <v>0.018639</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.280539</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>0.05218</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -13639,17 +13335,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities                                             340,000                         ‐</t>
+          <t>CASH FLOWS FROM (TO) OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
+          <t>Net income (loss) for the year $</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -13667,21 +13363,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H88" s="5" t="n">
+        <v>-0.2223</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>2.760725</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>0.018639</v>
+        <v>1.05654</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>0.280539</v>
+        <v>-4.414811</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -13722,12 +13414,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.      BASIS OF PREPARATION</t>
+          <t>Share‐based compensation                                                                                           ‐          117,040</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>interpretations of the International Financial Reporting Interpretations Committee (“IFRIC”). subsidiary; and were authorized for issue by the Audit Committee and Board of Directors on April</t>
+          <t>Unrealized (gain) loss on marketable securities</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -13757,10 +13449,10 @@
         </is>
       </c>
       <c r="J89" s="5" t="n">
-        <v>0.002019</v>
+        <v>-1.173043</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>2.5e-05</v>
+        <v>4.348743</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -13801,19 +13493,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Add adjustments</t>
+          <t>Write‐off of exploration and evaluation assets                                        8,100                         ‐</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gain on sale of exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -13829,21 +13517,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H90" s="5" t="n">
-        <v>-0.00753</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>-1.122174</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>-0.00056</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.002832</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -13884,15 +13572,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Add adjustments</t>
+          <t>CASH FLOWS FROM (TO) INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Unrealized loss on property payment receivable</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Net cash from investing activities</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -13913,18 +13605,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n">
-        <v>0.005679</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0.066955</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>0.140588</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -13965,12 +13655,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) INVESTING ACTIVITIES</t>
+          <t>Net cash provided by financing activities                                             340,000                         ‐</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Proceeds on sale of exploration and evaluation asset</t>
+          <t>Net increase (decrease) in cash and cash equivalents during the year</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -13989,21 +13679,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H92" s="5" t="n">
-        <v>0.195473</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>-0.049757</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>0.2619</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -14044,17 +13734,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) INVESTING ACTIVITIES</t>
+          <t>Net cash provided by financing activities                                             340,000                         ‐</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -14067,24 +13757,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G93" s="5" t="n">
-        <v>-1.156295</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>-0.083551</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>-0.500925</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>0.068396</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>0.018639</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -14125,41 +13817,49 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
+          <t>Net cash provided by financing activities                                             340,000                         ‐</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of share capital</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>1.265004</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>0.38964</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>0.018639</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>0.280539</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -14200,45 +13900,45 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
+          <t>2.      BASIS OF PREPARATION</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>interpretations of the International Financial Reporting Interpretations Committee (“IFRIC”). subsidiary; and were authorized for issue by the Audit Committee and Board of Directors on April</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F95" s="5" t="n">
-        <v>-0.00636</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>-0.025217</v>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>-0.003531</v>
-      </c>
-      <c r="I95" s="5" t="n">
-        <v>-0.008938</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>2.5e-05</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -14279,17 +13979,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM (TO) OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Net income for the year $</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -14297,22 +13997,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F96" s="5" t="n">
-        <v>0.49364</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>1.239787</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>0.336469</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I96" s="5" t="n">
-        <v>0.380702</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.760725</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>1.05654</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -14358,15 +14062,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
+          <t>Add adjustments</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Net change in cash and cash equivalents during the year</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Gain on sale of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -14377,14 +14085,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G97" s="5" t="n">
-        <v>-0.175346</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0.127197</v>
+        <v>-0.00753</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.116631</v>
+        <v>-1.122174</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -14435,40 +14145,40 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
+          <t>Add adjustments</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Unrealized (gain) loss on property payment receivable</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>0.553433</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>0.233176</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>0.05783</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.185027</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005679</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>-0.005679</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -14514,35 +14224,35 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM (TO) INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Proceeds on sale of exploration and evaluation asset</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F99" s="5" t="n">
-        <v>0.233176</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>0.05783</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.185027</v>
+        <v>0.195473</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>0.068396</v>
+        <v>0.075</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -14593,15 +14303,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Add adjustments</t>
+          <t>CASH FLOWS FROM (TO) INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Unrealized loss (gain) on marketable securities</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Net cash from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -14612,21 +14326,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G100" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>-0.013146</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>-0.30372</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>0.066955</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -14672,12 +14386,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Advance from optionee</t>
+          <t>Proceeds from issuance of share capital</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -14686,23 +14400,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.000852</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.265004</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0.38964</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -14753,35 +14461,35 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                                     321,570                         ‐</t>
+          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.00636</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.025217</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>-0.003531</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>-0.008938</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -14832,17 +14540,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                                     321,570                         ‐</t>
+          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Write‐off of exploration and evaluation assets</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -14851,20 +14559,16 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.021201</v>
+        <v>0.49364</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.026542</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.239787</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.336469</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0.380702</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -14915,12 +14619,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                                     321,570                         ‐</t>
+          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Net decrease in cash and cash equivalents during the year</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -14930,25 +14634,21 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.004632</v>
+        <v>-0.320257</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.001782</v>
+        <v>-0.175346</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="5" t="n">
+        <v>-0.116631</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>-0.049757</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -14994,40 +14694,38 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Changes in non‐cash working capital items</t>
+          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Advance from optionee</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
-        <v>-0.023458</v>
+        <v>0.553433</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>-0.000852</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.233176</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>0.05783</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>0.185027</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>0.068396</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -15073,40 +14771,38 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Exploration and evaluation asset recoveries                                                                          ‐           23,981</t>
+          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Interest received</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.004632</v>
+        <v>0.233176</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.001782</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05783</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>0.185027</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>0.068396</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>0.018639</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -15152,39 +14848,37 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Exploration and evaluation asset recoveries                                                                          ‐           23,981</t>
+          <t>Add adjustments</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Unrealized loss on property payment receivable</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F107" s="5" t="n">
-        <v>-0.502129</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>-1.156295</v>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I107" s="5" t="n">
+        <v>0.005679</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -15235,35 +14929,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM (TO) INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Net decrease in cash and cash equivalents during the year</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F108" s="5" t="n">
-        <v>-0.320257</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>-0.175346</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.156295</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>-0.083551</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>-0.500925</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -15309,17 +15005,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM (TO) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Business development and property investigation $</t>
+          <t>Net change in cash and cash equivalents during the year</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -15333,20 +15029,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G109" s="5" t="n">
+        <v>-0.175346</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0.127197</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>-0.116631</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -15373,30 +15063,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O109" s="5" t="n">
-        <v>0.002199</v>
-      </c>
-      <c r="P109" s="5" t="n">
-        <v>0.000855</v>
-      </c>
-      <c r="Q109" s="5" t="n">
-        <v>0.006712</v>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Add adjustments</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Corporate communications (Note 14)</t>
+          <t>Unrealized loss (gain) on marketable securities</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -15410,15 +15106,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G110" s="5" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>-0.013146</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -15445,119 +15137,135 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N110" s="5" t="n">
-        <v>0.244773</v>
-      </c>
-      <c r="O110" s="5" t="n">
-        <v>0.250089</v>
-      </c>
-      <c r="P110" s="5" t="n">
-        <v>0.234946</v>
-      </c>
-      <c r="Q110" s="5" t="n">
-        <v>0.327135</v>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Listing and transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Advance from optionee</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F111" s="5" t="n">
-        <v>0.012548</v>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.013272</v>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>0.013181</v>
-      </c>
-      <c r="I111" s="5" t="n">
-        <v>0.01237</v>
-      </c>
-      <c r="J111" s="5" t="n">
-        <v>0.014293</v>
-      </c>
-      <c r="K111" s="5" t="n">
-        <v>0.014239</v>
+        <v>-0.000852</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M111" s="5" t="n">
-        <v>0.016549</v>
-      </c>
-      <c r="N111" s="5" t="n">
-        <v>0.024621</v>
-      </c>
-      <c r="O111" s="5" t="n">
-        <v>0.02991</v>
-      </c>
-      <c r="P111" s="5" t="n">
-        <v>0.021282</v>
-      </c>
-      <c r="Q111" s="5" t="n">
-        <v>0.041864</v>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share‐based compensation                                                     321,570                         ‐</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Management fees (Note 14)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Unrealized loss on marketable securities</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="5" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.0016</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -15589,38 +15297,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N112" s="5" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="O112" s="5" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="P112" s="5" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="Q112" s="5" t="n">
-        <v>0.078</v>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share‐based compensation                                                     321,570                         ‐</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Office and administrative</t>
+          <t>Write‐off of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -15629,79 +15345,89 @@
         </is>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.066751</v>
+        <v>0.021201</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.076516</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>0.045803</v>
-      </c>
-      <c r="I113" s="5" t="n">
-        <v>0.056964</v>
-      </c>
-      <c r="J113" s="5" t="n">
-        <v>0.042096</v>
-      </c>
-      <c r="K113" s="5" t="n">
-        <v>0.048932</v>
+        <v>0.026542</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M113" s="5" t="n">
-        <v>0.06217</v>
-      </c>
-      <c r="N113" s="5" t="n">
-        <v>0.088751</v>
-      </c>
-      <c r="O113" s="5" t="n">
-        <v>0.090625</v>
-      </c>
-      <c r="P113" s="5" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="Q113" s="5" t="n">
-        <v>0.082258</v>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share‐based compensation                                                     321,570                         ‐</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Professional fees (Note 14)</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="5" t="n">
+        <v>-0.004632</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>-0.001782</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -15733,33 +15459,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N114" s="5" t="n">
-        <v>0.053596</v>
-      </c>
-      <c r="O114" s="5" t="n">
-        <v>0.038831</v>
-      </c>
-      <c r="P114" s="5" t="n">
-        <v>0.034346</v>
-      </c>
-      <c r="Q114" s="5" t="n">
-        <v>0.051617</v>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non‐cash working capital items</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 12 and 14)</t>
+          <t>Advance from optionee</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -15768,15 +15502,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F115" s="5" t="n">
+        <v>-0.023458</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>-0.000852</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -15808,54 +15538,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N115" s="5" t="n">
-        <v>0.678365</v>
-      </c>
-      <c r="O115" s="5" t="n">
-        <v>0.06335499999999999</v>
-      </c>
-      <c r="P115" s="5" t="n">
-        <v>0.575755</v>
-      </c>
-      <c r="Q115" s="5" t="n">
-        <v>0.016894</v>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Exploration and evaluation asset recoveries                                                                          ‐           23,981</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Interest received</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F116" s="5" t="n">
+        <v>0.004632</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.001782</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -15882,41 +15612,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M116" s="5" t="n">
-        <v>-1.256488</v>
-      </c>
-      <c r="N116" s="5" t="n">
-        <v>-1.1781</v>
-      </c>
-      <c r="O116" s="5" t="n">
-        <v>-0.553009</v>
-      </c>
-      <c r="P116" s="5" t="n">
-        <v>-1.031184</v>
-      </c>
-      <c r="Q116" s="5" t="n">
-        <v>-0.60448</v>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Exploration and evaluation asset recoveries                                                                          ‐           23,981</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -15925,70 +15665,88 @@
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>0.004632</v>
+        <v>-0.502129</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.001782</v>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>0.000884</v>
-      </c>
-      <c r="I117" s="5" t="n">
-        <v>0.000879</v>
-      </c>
-      <c r="J117" s="5" t="n">
-        <v>0.00056</v>
-      </c>
-      <c r="K117" s="5" t="n">
-        <v>0.002832</v>
+        <v>-1.156295</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M117" s="5" t="n">
-        <v>0.005596</v>
-      </c>
-      <c r="N117" s="5" t="n">
-        <v>0.041376</v>
-      </c>
-      <c r="O117" s="5" t="n">
-        <v>0.08643199999999999</v>
-      </c>
-      <c r="P117" s="5" t="n">
-        <v>0.163442</v>
-      </c>
-      <c r="Q117" s="5" t="n">
-        <v>0.049938</v>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of marketable securities (Note 5)</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>-0.34404</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>-0.275805</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -16025,45 +15783,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N118" s="5" t="n">
-        <v>0.00171</v>
-      </c>
-      <c r="O118" s="5" t="n">
-        <v>-0.023792</v>
-      </c>
-      <c r="P118" s="5" t="n">
-        <v>-0.020391</v>
-      </c>
-      <c r="Q118" s="5" t="n">
-        <v>0.280841</v>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Unrealized loss on marketable securities                                             9,600                        ‐</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities (Note 5)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write‐off of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0.010582</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.021201</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -16110,48 +15876,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P119" s="5" t="n">
-        <v>0.664375</v>
-      </c>
-      <c r="Q119" s="5" t="n">
-        <v>0.6585839999999999</v>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Unrealized loss on marketable securities                                             9,600                        ‐</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets (Note 8)</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>-0.026542</v>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>-0.061198</v>
-      </c>
-      <c r="I120" s="5" t="n">
-        <v>-1.340443</v>
+      <c r="E120" s="5" t="n">
+        <v>-0.005551</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>-0.004632</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -16168,17 +15940,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M120" s="5" t="n">
-        <v>-0.080497</v>
-      </c>
-      <c r="N120" s="5" t="n">
-        <v>-0.006845</v>
-      </c>
-      <c r="O120" s="5" t="n">
-        <v>-0.076555</v>
-      </c>
-      <c r="P120" s="5" t="n">
-        <v>-0.106386</v>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -16189,111 +15969,133 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Changes in non‐cash working capital items</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Other items total</t>
+          <t>Advance from Optionee</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="5" t="n">
+        <v>0.02431</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>-0.026169</v>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>-0.02636</v>
-      </c>
-      <c r="H121" s="5" t="n">
-        <v>-0.039638</v>
-      </c>
-      <c r="I121" s="5" t="n">
-        <v>3.029609</v>
-      </c>
-      <c r="J121" s="5" t="n">
-        <v>1.433495</v>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>-4.235851</v>
+        <v>-0.023458</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M121" s="5" t="n">
-        <v>-1.765841</v>
-      </c>
-      <c r="N121" s="5" t="n">
-        <v>-1.144054</v>
-      </c>
-      <c r="O121" s="5" t="n">
-        <v>-0.558462</v>
-      </c>
-      <c r="P121" s="5" t="n">
-        <v>0.70104</v>
-      </c>
-      <c r="Q121" s="5" t="n">
-        <v>0.989363</v>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) for the year $</t>
+          <t>Exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>-0.330088</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>-0.530742</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H122" s="5" t="n">
-        <v>-0.2223</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>2.760725</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>1.05654</v>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>-4.414811</v>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -16315,60 +16117,64 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P122" s="5" t="n">
-        <v>-0.330144</v>
-      </c>
-      <c r="Q122" s="5" t="n">
-        <v>0.384883</v>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Basic and diluted income (loss) per common share $</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation asset recoveries</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
+        <v>0.245592</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.023981</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>3e-08</v>
-      </c>
-      <c r="J123" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>-4e-08</v>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -16390,104 +16196,122 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="5" t="n">
-        <v>0</v>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest received</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>0.005551</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>65.810394</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>76.92957199999999</v>
-      </c>
-      <c r="H124" s="5" t="n">
-        <v>91.53444</v>
-      </c>
-      <c r="I124" s="5" t="n">
-        <v>96.975656</v>
-      </c>
-      <c r="J124" s="5" t="n">
-        <v>101.250084</v>
-      </c>
-      <c r="K124" s="5" t="n">
-        <v>107.701042</v>
+        <v>0.004632</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M124" s="5" t="n">
-        <v>123.065922</v>
-      </c>
-      <c r="N124" s="5" t="n">
-        <v>136.395198</v>
-      </c>
-      <c r="O124" s="5" t="n">
-        <v>146.541156</v>
-      </c>
-      <c r="P124" s="5" t="n">
-        <v>162.313119</v>
-      </c>
-      <c r="Q124" s="5" t="n">
-        <v>176.296042</v>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Loss on sale of marketable securities (Note 5)</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>-0.078945</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>-0.502129</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -16524,14 +16348,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N125" s="5" t="n">
-        <v>0.00171</v>
-      </c>
-      <c r="O125" s="5" t="n">
-        <v>-0.023792</v>
-      </c>
-      <c r="P125" s="5" t="n">
-        <v>-0.020391</v>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16542,44 +16372,50 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities (Note 5)</t>
+          <t>Net increase (decrease) in cash and cash equivalents during the year</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>-0.0016</v>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>0.013146</v>
-      </c>
-      <c r="I126" s="5" t="n">
-        <v>3.09958</v>
-      </c>
-      <c r="J126" s="5" t="n">
-        <v>1.173043</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>-4.348743</v>
+      <c r="E126" s="5" t="n">
+        <v>0.183686</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>-0.320257</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -16596,11 +16432,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O126" s="5" t="n">
-        <v>-0.602447</v>
-      </c>
-      <c r="P126" s="5" t="n">
-        <v>0.664375</v>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16616,12 +16456,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Flow-through share premium received (Note 12)</t>
+          <t>Business development and property investigation $</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -16676,17 +16516,13 @@
         </is>
       </c>
       <c r="O127" s="5" t="n">
-        <v>0.0579</v>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002199</v>
+      </c>
+      <c r="P127" s="5" t="n">
+        <v>0.000855</v>
+      </c>
+      <c r="Q127" s="5" t="n">
+        <v>0.006712</v>
       </c>
     </row>
     <row r="128">
@@ -16697,32 +16533,34 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Corporate communications (Note 14)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F128" s="5" t="n">
-        <v>-0.275805</v>
-      </c>
-      <c r="G128" s="5" t="n">
-        <v>-0.591817</v>
-      </c>
-      <c r="H128" s="5" t="n">
-        <v>-0.2223</v>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -16744,22 +16582,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M128" s="5" t="n">
-        <v>-3.022329</v>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N128" s="5" t="n">
-        <v>-2.322154</v>
+        <v>0.244773</v>
       </c>
       <c r="O128" s="5" t="n">
-        <v>-1.111471</v>
+        <v>0.250089</v>
       </c>
       <c r="P128" s="5" t="n">
-        <v>-0.330144</v>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.234946</v>
+      </c>
+      <c r="Q128" s="5" t="n">
+        <v>0.327135</v>
       </c>
     </row>
     <row r="129">
@@ -16770,69 +16608,57 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Listing and transfer agent fees</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0.012395</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0</v>
+        <v>0.012548</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.013272</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013181</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>0.014293</v>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>0.014239</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>0.012603</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.016549</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.024621</v>
       </c>
       <c r="O129" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.02991</v>
       </c>
       <c r="P129" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021282</v>
+      </c>
+      <c r="Q129" s="5" t="n">
+        <v>0.041864</v>
       </c>
     </row>
     <row r="130">
@@ -16848,10 +16674,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Business development and property investigation (Note 14) $</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>Management fees (Note 14)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -16898,20 +16728,16 @@
         </is>
       </c>
       <c r="N130" s="5" t="n">
-        <v>0.011994</v>
+        <v>0.076</v>
       </c>
       <c r="O130" s="5" t="n">
-        <v>0.002199</v>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.078</v>
+      </c>
+      <c r="P130" s="5" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="Q130" s="5" t="n">
+        <v>0.078</v>
       </c>
     </row>
     <row r="131">
@@ -16922,69 +16748,57 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities (Note 5)</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office and administrative</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>0.063568</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.066751</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>-0.0016</v>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.076516</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>0.045803</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>0.056964</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>0.042096</v>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>0.048932</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>0.048152</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>-1.69094</v>
+        <v>0.06217</v>
       </c>
       <c r="N131" s="5" t="n">
-        <v>-1.180295</v>
+        <v>0.088751</v>
       </c>
       <c r="O131" s="5" t="n">
-        <v>-0.602447</v>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.090625</v>
+      </c>
+      <c r="P131" s="5" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="Q131" s="5" t="n">
+        <v>0.082258</v>
       </c>
     </row>
     <row r="132">
@@ -17000,20 +16814,28 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Business development and property investigation (Note 13) $</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Professional fees (Note 14)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F132" s="5" t="n">
-        <v>0.063397</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>0.013004</v>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -17040,26 +16862,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M132" s="5" t="n">
-        <v>0.081841</v>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N132" s="5" t="n">
-        <v>0.011994</v>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.053596</v>
+      </c>
+      <c r="O132" s="5" t="n">
+        <v>0.038831</v>
+      </c>
+      <c r="P132" s="5" t="n">
+        <v>0.034346</v>
+      </c>
+      <c r="Q132" s="5" t="n">
+        <v>0.051617</v>
       </c>
     </row>
     <row r="133">
@@ -17075,7 +16893,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Corporate communications (Note 13)</t>
+          <t>Share-based compensation (Notes 12 and 14)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -17084,11 +16902,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F133" s="5" t="n">
-        <v>0.026683</v>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>0.05188</v>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -17115,26 +16937,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M133" s="5" t="n">
-        <v>0.177756</v>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N133" s="5" t="n">
-        <v>0.244773</v>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.678365</v>
+      </c>
+      <c r="O133" s="5" t="n">
+        <v>0.06335499999999999</v>
+      </c>
+      <c r="P133" s="5" t="n">
+        <v>0.575755</v>
+      </c>
+      <c r="Q133" s="5" t="n">
+        <v>0.016894</v>
       </c>
     </row>
     <row r="134">
@@ -17150,12 +16968,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Management fees (Note 13)</t>
+          <t>Loss from operations</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -17163,26 +16981,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F134" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>0.06045</v>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="5" t="n">
+        <v>-0.268884</v>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>-0.376955</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -17195,25 +17013,19 @@
         </is>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.066</v>
+        <v>-1.256488</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.1781</v>
+      </c>
+      <c r="O134" s="5" t="n">
+        <v>-0.553009</v>
+      </c>
+      <c r="P134" s="5" t="n">
+        <v>-1.031184</v>
+      </c>
+      <c r="Q134" s="5" t="n">
+        <v>-0.60448</v>
       </c>
     </row>
     <row r="135">
@@ -17224,75 +17036,57 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Professional fees (Note 13)</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.005551</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>0.020257</v>
+        <v>0.004632</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.028765</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001782</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>0.000884</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0.000879</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>0.00056</v>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>0.002832</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>0.002049</v>
       </c>
       <c r="M135" s="5" t="n">
-        <v>0.025573</v>
+        <v>0.005596</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>0.053596</v>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.041376</v>
+      </c>
+      <c r="O135" s="5" t="n">
+        <v>0.08643199999999999</v>
+      </c>
+      <c r="P135" s="5" t="n">
+        <v>0.163442</v>
+      </c>
+      <c r="Q135" s="5" t="n">
+        <v>0.049938</v>
       </c>
     </row>
     <row r="136">
@@ -17303,12 +17097,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 11)</t>
+          <t>Gain (loss) on sale of marketable securities (Note 5)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -17342,36 +17136,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M136" s="5" t="n">
-        <v>0.826599</v>
+      <c r="K136" s="5" t="n">
+        <v>0.11816</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>-0.024626</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N136" s="5" t="n">
-        <v>0.678365</v>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00171</v>
+      </c>
+      <c r="O136" s="5" t="n">
+        <v>-0.023792</v>
+      </c>
+      <c r="P136" s="5" t="n">
+        <v>-0.020391</v>
+      </c>
+      <c r="Q136" s="5" t="n">
+        <v>0.280841</v>
       </c>
     </row>
     <row r="137">
@@ -17382,12 +17168,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Business development and property investigation (Note 12) $</t>
+          <t>Unrealized gain on marketable securities (Note 5)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -17401,20 +17187,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G137" s="5" t="n">
-        <v>0.013004</v>
-      </c>
-      <c r="H137" s="5" t="n">
-        <v>0.029445</v>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I137" s="5" t="n">
-        <v>0.023668</v>
+        <v>3.09958</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>0.08255700000000001</v>
-      </c>
-      <c r="K137" s="5" t="n">
-        <v>0.013965</v>
+        <v>1.173043</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -17436,15 +17228,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P137" s="5" t="n">
+        <v>0.664375</v>
+      </c>
+      <c r="Q137" s="5" t="n">
+        <v>0.6585839999999999</v>
       </c>
     </row>
     <row r="138">
@@ -17455,12 +17243,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Corporate communications</t>
+          <t>Write-off of exploration and evaluation assets (Note 8)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -17474,51 +17262,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>0.027797</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>0.008921999999999999</v>
+      <c r="G138" s="5" t="n">
+        <v>-0.026542</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>-0.061198</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>-1.340443</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M138" s="5" t="n">
+        <v>-0.080497</v>
+      </c>
+      <c r="N138" s="5" t="n">
+        <v>-0.006845</v>
+      </c>
+      <c r="O138" s="5" t="n">
+        <v>-0.076555</v>
+      </c>
+      <c r="P138" s="5" t="n">
+        <v>-0.106386</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -17534,73 +17312,53 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Management fees (Note 12)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other items total</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>-0.005031</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>-0.026169</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.06045</v>
+        <v>-0.02636</v>
       </c>
       <c r="H139" s="5" t="n">
-        <v>0.06</v>
+        <v>-0.039638</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>0.06</v>
+        <v>3.029609</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>0.066</v>
+        <v>1.433495</v>
       </c>
       <c r="K139" s="5" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.235851</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>0.029873</v>
+      </c>
+      <c r="M139" s="5" t="n">
+        <v>-1.765841</v>
+      </c>
+      <c r="N139" s="5" t="n">
+        <v>-1.144054</v>
+      </c>
+      <c r="O139" s="5" t="n">
+        <v>-0.558462</v>
+      </c>
+      <c r="P139" s="5" t="n">
+        <v>0.70104</v>
+      </c>
+      <c r="Q139" s="5" t="n">
+        <v>0.989363</v>
       </c>
     </row>
     <row r="140">
@@ -17611,17 +17369,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Professional fees (Note 12)</t>
+          <t>Comprehensive income (loss) for the year $</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -17634,20 +17392,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G140" s="5" t="n">
-        <v>0.028765</v>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H140" s="5" t="n">
-        <v>0.021591</v>
+        <v>-0.2223</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>0.022366</v>
+        <v>2.760725</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>0.027172</v>
+        <v>1.05654</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>0.026902</v>
+        <v>-4.414811</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -17669,15 +17429,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P140" s="5" t="n">
+        <v>-0.330144</v>
+      </c>
+      <c r="Q140" s="5" t="n">
+        <v>0.384883</v>
       </c>
     </row>
     <row r="141">
@@ -17688,17 +17444,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                                                                 ‐         117,040</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
+          <t>Basic and diluted income (loss) per common share $</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -17716,21 +17472,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>3e-08</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>-0.376955</v>
+        <v>1e-08</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>-0.17896</v>
+        <v>-4e-08</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -17752,15 +17504,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -17776,68 +17524,52 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gain on sale of marketable securities (Note 5)</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>51.755463</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>65.810394</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>76.92957199999999</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>91.53444</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>0.147419</v>
+        <v>96.975656</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>0.259892</v>
+        <v>101.250084</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>0.11816</v>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>107.701042</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>110.411248</v>
+      </c>
+      <c r="M142" s="5" t="n">
+        <v>123.065922</v>
+      </c>
+      <c r="N142" s="5" t="n">
+        <v>136.395198</v>
+      </c>
+      <c r="O142" s="5" t="n">
+        <v>146.541156</v>
+      </c>
+      <c r="P142" s="5" t="n">
+        <v>162.313119</v>
+      </c>
+      <c r="Q142" s="5" t="n">
+        <v>176.296042</v>
       </c>
     </row>
     <row r="143">
@@ -17848,12 +17580,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Corporate communications (Note 12)</t>
+          <t>Loss on sale of marketable securities (Note 5)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -17867,14 +17599,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G143" s="5" t="n">
-        <v>0.05188</v>
-      </c>
-      <c r="H143" s="5" t="n">
-        <v>0.012642</v>
-      </c>
-      <c r="I143" s="5" t="n">
-        <v>0.012696</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -17896,20 +17634,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N143" s="5" t="n">
+        <v>0.00171</v>
+      </c>
+      <c r="O143" s="5" t="n">
+        <v>-0.023792</v>
+      </c>
+      <c r="P143" s="5" t="n">
+        <v>-0.020391</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -17925,12 +17657,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10)</t>
+          <t>Unrealized gain (loss) on marketable securities (Note 5)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -17945,30 +17677,22 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.32157</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.0016</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>0.013146</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>0.08082</v>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.09958</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>1.173043</v>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>-4.348743</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>0.06637</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -17980,15 +17704,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O144" s="5" t="n">
+        <v>-0.602447</v>
+      </c>
+      <c r="P144" s="5" t="n">
+        <v>0.664375</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -18004,19 +17724,15 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Flow-through share premium received (Note 12)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -18027,14 +17743,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G145" s="5" t="n">
-        <v>-0.565457</v>
-      </c>
-      <c r="H145" s="5" t="n">
-        <v>-0.182662</v>
-      </c>
-      <c r="I145" s="5" t="n">
-        <v>-0.268884</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -18061,10 +17783,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O145" s="5" t="n">
+        <v>0.0579</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -18090,65 +17810,53 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Gain on sale of exploration and evaluation assets (Note 8)</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>-0.34404</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>-0.275805</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>-0.591817</v>
       </c>
       <c r="H146" s="5" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I146" s="5" t="n">
-        <v>1.122174</v>
+        <v>-0.2223</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K146" s="5" t="n">
+        <v>-4.414811</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>-0.248632</v>
+      </c>
+      <c r="M146" s="5" t="n">
+        <v>-3.022329</v>
+      </c>
+      <c r="N146" s="5" t="n">
+        <v>-2.322154</v>
+      </c>
+      <c r="O146" s="5" t="n">
+        <v>-1.111471</v>
+      </c>
+      <c r="P146" s="5" t="n">
+        <v>-0.330144</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -18164,34 +17872,30 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                               321,570                        ‐</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>-0.249636</v>
+        <v>0</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>-0.565457</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -18203,35 +17907,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K147" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="N147" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="O147" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="P147" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -18247,12 +17939,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Write‐off of exploration and evaluation assets (Note 8)</t>
+          <t>Business development and property investigation (Note 14) $</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -18261,58 +17953,1760 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F148" s="5" t="n">
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="5" t="n">
+        <v>0.011994</v>
+      </c>
+      <c r="O148" s="5" t="n">
+        <v>0.002199</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable securities (Note 5)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="n">
+        <v>-1.69094</v>
+      </c>
+      <c r="N149" s="5" t="n">
+        <v>-1.180295</v>
+      </c>
+      <c r="O149" s="5" t="n">
+        <v>-0.602447</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Business development and property investigation (Note 13) $</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" s="5" t="n">
+        <v>0.064902</v>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>0.063397</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.013004</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="n">
+        <v>0.081841</v>
+      </c>
+      <c r="N150" s="5" t="n">
+        <v>0.011994</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Corporate communications (Note 13)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" s="5" t="n">
+        <v>0.039757</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>0.026683</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.05188</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M151" s="5" t="n">
+        <v>0.177756</v>
+      </c>
+      <c r="N151" s="5" t="n">
+        <v>0.244773</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Management fees (Note 13)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>0.069675</v>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.06045</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M152" s="5" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="N152" s="5" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Professional fees (Note 13)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>0.030632</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>0.020257</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.028765</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M153" s="5" t="n">
+        <v>0.025573</v>
+      </c>
+      <c r="N153" s="5" t="n">
+        <v>0.053596</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 11)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M154" s="5" t="n">
+        <v>0.826599</v>
+      </c>
+      <c r="N154" s="5" t="n">
+        <v>0.678365</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Business development and property investigation (Note 12) $</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.013004</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>0.029445</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>0.023668</v>
+      </c>
+      <c r="J155" s="5" t="n">
+        <v>0.08255700000000001</v>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>0.013965</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>0.029707</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Corporate communications</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>0.027797</v>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>0.008921999999999999</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>0.006296</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Management fees (Note 12)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.06045</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J157" s="5" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Professional fees (Note 12)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.028765</v>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>0.021591</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>0.022366</v>
+      </c>
+      <c r="J158" s="5" t="n">
+        <v>0.027172</v>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>0.026902</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>0.020217</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Share‐based compensation                                                95,530                        ‐</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>-0.17896</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>-0.278505</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Write‐off of exploration and evaluation assets (Note 8)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" s="5" t="n">
+        <v>-0.010582</v>
+      </c>
+      <c r="F160" s="5" t="n">
         <v>-0.021201</v>
       </c>
-      <c r="G148" s="5" t="n">
+      <c r="G160" s="5" t="n">
         <v>-0.026542</v>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>-0.01392</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Share‐based compensation                                                                                 ‐         117,040</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="n">
+        <v>-0.376955</v>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>-0.17896</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Gain on sale of marketable securities (Note 5)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>0.147419</v>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>0.259892</v>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>0.11816</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Corporate communications (Note 12)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.05188</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>0.012642</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>0.012696</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>0.027797</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 10)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>0.08082</v>
+      </c>
+      <c r="J164" s="5" t="n">
+        <v>0.11704</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Gain on sale of exploration and evaluation assets (Note 8)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>1.122174</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Comprehensive income for the year $</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>2.760725</v>
+      </c>
+      <c r="J166" s="5" t="n">
+        <v>1.05654</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Basic and diluted income per common share $</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="J167" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>-0.565457</v>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>-0.182662</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>-0.268884</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Share‐based compensation                                               321,570                        ‐</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>-0.249636</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>-0.565457</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Share‐based compensation                                                                                 ‐          58,080</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n">
+        <v>-0.339009</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>-0.249636</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
         <is>
           <t>-</t>
         </is>
